--- a/papers/P005/P005_工程复现问题清单_v1.xlsx
+++ b/papers/P005/P005_工程复现问题清单_v1.xlsx
@@ -55,13 +55,13 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -71,186 +71,254 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="100" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
+    <col min="3" max="3" width="103" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">关键问题</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">简明答案</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="91" customHeight="1">
-      <c r="A2" s="0" t="inlineStr">
+    <row r="2" ht="93" customHeight="1">
+      <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">市场环境究竟是什么？</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">是行情网页、新闻还是市场状态描述？内容从哪里来？</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">不是网页，也不是原始K线全文。系统先汇总当时可知的收益、波动、上涨股票占比、量能、板块轮动等数值指标（短10/中63/长252日），再用Llama-3.3-70B-Instruct（温度0）转成“短期/中期/长期/总体”四段英文市场描述，供LLM参考。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="91" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="93" customHeight="1">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LLM底座与职责</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">市场环境解释和因子生成用的是同一个模型吗？</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">两者分工不同：Llama-3.3-70B-Instruct把市场数值统计整理成语言描述；负责多轮因子提案、工具交互和搜索策略的是Qwen3-4B，后者通过离线GRPO更新参数，测试日只执行固定模型策略。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="103" customHeight="1">
+      <c r="A4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">市场信息怎样与因子池结合？</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">市场描述和当前因子池是一起写进Prompt吗？</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">是，但各有用途：每日User Prompt填写市场文字q_t、种子或前日沿用因子清单S_t、可用DSL算子O及时间窗口；System Prompt约束工具和表达式。进入多轮后，当前保留池摘要和最近尝试记录再作为反馈文本给LLM；不是把两者先算成一个神秘的数值特征。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="91" customHeight="1">
-      <c r="A4" s="0" t="inlineStr">
+    <row r="5" ht="93" customHeight="1">
+      <c r="A5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">当前因子池指什么？</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">“当前因子池”里实际保存的是什么？</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">是程序维护的Retained Factor Pool（当前保留的因子集合），初始可来自种子/前日沿用因子，之后随测试结果改变。反馈给LLM的摘要含池评分、成员公式、因子类别、单因子分数、IC和RankIC；它不等于股票池或一张行情页面。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="91" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6" ht="93" customHeight="1">
+      <c r="A6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">初始任务与因子生成形式</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">与P001研究假设、P002 Python函数相比，P005到底输入和输出什么？</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">每天以市场描述q_t、保留因子池S_t与DSL算子/时窗定义搜索上下文，而非要求人工逐条给出Research Idea；Qwen3-4B每轮提出若干DSL因子公式和类别标签，之后由工具执行与打分，不是生成一整份Python工程。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="93" customHeight="1">
+      <c r="A7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">池级边际贡献的计算单位</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">是单个因子的边际，还是一次加入整批因子的增量？</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">每轮可一次提出多个候选，但Pool Updater逐个判断：计算“加入当前候选前后”整池得分变化ΔΓ=Γ(P∪{f})−Γ(P)（满池则比较替换某成员后的变化）。所以操作单位是单候选，评价对象是整池；不能把单因子IC高直接等同于值得保留。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="91" customHeight="1">
-      <c r="A6" s="0" t="inlineStr">
+    <row r="8" ht="93" customHeight="1">
+      <c r="A8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">整个池怎么得到分数？</t>
         </is>
       </c>
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">为何加入一个好因子反而可能被拒绝？</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">先用近期约126个交易日的历史数据，对池内因子截面Rank信号拟合非负岭回归式组合权重，汇总成Meta-alpha，再算组合IC、RankIC及多样性/稳定性等池指标。新因子可能与现有因子重复，单项IC虽高却不改善组合，因此边际池收益≤0会被拒绝。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="91" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9" ht="93" customHeight="1">
+      <c r="A9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">质量检查与评分层次</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">什么检查先于池级边际决定，如何区分有效因子和有价值入池？</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">factor_evaluator先校验DSL语法与计算可行性、覆盖率及近期单因子IC/RankIC/稳定性；Pool Updater再判断新增候选是否提升整体加权池表现。单候选可用不等于值得入池，不能把两层评分混为一谈。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="103" customHeight="1">
+      <c r="A10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">池状态具体怎样更新？</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">谁执行接收、剔除、替换？是LLM自己做吗？</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">LLM提出DSL公式及类别→factor_evaluator语法校验、运行并算单因子IC/RankIC/稳定性/覆盖率→外部Pool Updater先过滤无效候选，再按ΔΓ选择加入/拒绝；满池则尝试替换最弱或最冗余成员。更新的是程序管理的因子列表，不是LLM参数。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="91" customHeight="1">
-      <c r="A8" s="0" t="inlineStr">
+    <row r="11" ht="93" customHeight="1">
+      <c r="A11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">多轮反馈怎么闭环？</t>
         </is>
       </c>
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">更新池后，下一轮LLM到底看见什么？</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">工具把三类文本反馈接回对话：①当轮每个候选的评分、接收/拒绝、边际提升与相似度；②最近尝试过的因子FIFO记录；③当前池的成员和池得分。下一轮LLM据此继续生成或修改，而非盲目重复第一次Prompt。</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="91" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12" ht="103" customHeight="1">
+      <c r="A12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">GRPO本质是什么？</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">GRPO（你写的GPRO）具体如何学习，改的是哪里？</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">GRPO=Group Relative Policy Optimization，组相对策略优化。对同一历史市场情境采样多条完整“提议→工具→改池”轨迹；用各轨迹最终因子池在未来窗口的组合IC/RankIC构造奖励，按组内相对成绩形成优势，再通过梯度优化提高好轨迹的生成概率。不训练单独Critic；离线阶段真正更新Qwen3-4B的模型参数。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="91" customHeight="1">
-      <c r="A10" s="0" t="inlineStr">
+    <row r="13" ht="93" customHeight="1">
+      <c r="A13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">训练和实际使用怎样区分？</t>
         </is>
       </c>
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">既然用未来收益打分，会不会在每天预测时偷看未来？</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">训练时允许Reward Manager事后看未来21/63日窗口，监督整条历史搜索轨迹；部署/样本外每个交易日仅输入当日可知市场描述、历史行情与保留池，训练完成的LLM权重保持不变，只更新因子池。以上是论文流程口径，尚未独立运行代码审计。</t>
         </is>
       </c>
     </row>
+    <row r="14" ht="93" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">公开实现与复现边界</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">这是实际跑通的源码结论，还是论文叙述？</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">当前依据AlphaPilot论文§3–5及附录核查输入、工具、池更新与GRPO，尚未核实可直接运行的完整官方工程，更未独立复现训练或回测。论文中的流程不等于源码行为已经验证。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C10"/>
+  <autoFilter ref="A1:C14"/>
 </worksheet>
 </file>
--- a/papers/P005/P005_工程复现问题清单_v1.xlsx
+++ b/papers/P005/P005_工程复现问题清单_v1.xlsx
@@ -36,7 +36,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor rgb="FFF2F5F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -55,13 +55,13 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -72,15 +72,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="25"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="54" customWidth="1"/>
-    <col min="3" max="3" width="103" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="3" max="3" width="92" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
@@ -97,7 +97,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="93" customHeight="1">
+    <row r="2" ht="94" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">市场环境究竟是什么？</t>
@@ -114,7 +114,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="93" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LLM底座与职责</t>
@@ -131,7 +131,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="103" customHeight="1">
+    <row r="4" ht="94" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">市场信息怎样与因子池结合？</t>
@@ -148,7 +148,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="93" customHeight="1">
+    <row r="5" ht="94" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">当前因子池指什么？</t>
@@ -165,7 +165,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="93" customHeight="1">
+    <row r="6" ht="94" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">初始任务与因子生成形式</t>
@@ -182,7 +182,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="93" customHeight="1">
+    <row r="7" ht="94" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">池级边际贡献的计算单位</t>
@@ -199,7 +199,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="93" customHeight="1">
+    <row r="8" ht="94" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">整个池怎么得到分数？</t>
@@ -216,7 +216,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="93" customHeight="1">
+    <row r="9" ht="94" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">质量检查与评分层次</t>
@@ -233,7 +233,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="103" customHeight="1">
+    <row r="10" ht="94" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">池状态具体怎样更新？</t>
@@ -250,7 +250,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="93" customHeight="1">
+    <row r="11" ht="94" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">多轮反馈怎么闭环？</t>
@@ -267,58 +267,75 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="103" customHeight="1">
+    <row r="12" ht="94" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
+          <t xml:space="preserve">调度与优化对象</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">P005会像P006那样用Bandit决定改因子还是改预测模型吗？</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve">不会。P005的Qwen3-4B多轮提出DSL因子和工具调用，Pool Updater按池级边际贡献增删候选；外部代码执行筛选，离线GRPO优化LLM的搜索策略参数。没有P006式二臂Factor/Model调度器，也不让LLM交替研发独立的下游预测模型架构。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="108" customHeight="1">
+      <c r="A13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">GRPO本质是什么？</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr" s="0">
+      <c r="B13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">GRPO（你写的GPRO）具体如何学习，改的是哪里？</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr" s="0">
+      <c r="C13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">GRPO=Group Relative Policy Optimization，组相对策略优化。对同一历史市场情境采样多条完整“提议→工具→改池”轨迹；用各轨迹最终因子池在未来窗口的组合IC/RankIC构造奖励，按组内相对成绩形成优势，再通过梯度优化提高好轨迹的生成概率。不训练单独Critic；离线阶段真正更新Qwen3-4B的模型参数。</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="93" customHeight="1">
-      <c r="A13" t="inlineStr" s="2">
+    <row r="14" ht="94" customHeight="1">
+      <c r="A14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">训练和实际使用怎样区分？</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr" s="2">
+      <c r="B14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">既然用未来收益打分，会不会在每天预测时偷看未来？</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr" s="2">
+      <c r="C14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">训练时允许Reward Manager事后看未来21/63日窗口，监督整条历史搜索轨迹；部署/样本外每个交易日仅输入当日可知市场描述、历史行情与保留池，训练完成的LLM权重保持不变，只更新因子池。以上是论文流程口径，尚未独立运行代码审计。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="93" customHeight="1">
-      <c r="A14" t="inlineStr" s="0">
+    <row r="15" ht="82" customHeight="1">
+      <c r="A15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">公开实现与复现边界</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr" s="0">
+      <c r="B15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">这是实际跑通的源码结论，还是论文叙述？</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr" s="0">
+      <c r="C15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">当前依据AlphaPilot论文§3–5及附录核查输入、工具、池更新与GRPO，尚未核实可直接运行的完整官方工程，更未独立复现训练或回测。论文中的流程不等于源码行为已经验证。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C14"/>
+  <autoFilter ref="A1:C15"/>
 </worksheet>
 </file>
--- a/papers/P005/P005_工程复现问题清单_v1.xlsx
+++ b/papers/P005/P005_工程复现问题清单_v1.xlsx
@@ -30,13 +30,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF142B46"/>
+        <fgColor rgb="FF122C45"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F5F9"/>
+        <fgColor rgb="FFF0F5FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -55,13 +55,13 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -75,12 +75,12 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="53" customWidth="1"/>
-    <col min="3" max="3" width="92" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="3" width="94" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
@@ -97,7 +97,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="94" customHeight="1">
+    <row r="2" ht="88" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">市场环境究竟是什么？</t>
@@ -114,7 +114,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="94" customHeight="1">
+    <row r="3" ht="88" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LLM底座与职责</t>
@@ -131,7 +131,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="94" customHeight="1">
+    <row r="4" ht="100" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">市场信息怎样与因子池结合？</t>
@@ -148,7 +148,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="94" customHeight="1">
+    <row r="5" ht="88" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">当前因子池指什么？</t>
@@ -165,7 +165,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="94" customHeight="1">
+    <row r="6" ht="88" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">初始任务与因子生成形式</t>
@@ -182,7 +182,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="94" customHeight="1">
+    <row r="7" ht="88" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">池级边际贡献的计算单位</t>
@@ -199,7 +199,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="94" customHeight="1">
+    <row r="8" ht="124" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">整个池怎么得到分数？</t>
@@ -212,11 +212,11 @@
       </c>
       <c r="C8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">先用近期约126个交易日的历史数据，对池内因子截面Rank信号拟合非负岭回归式组合权重，汇总成Meta-alpha，再算组合IC、RankIC及多样性/稳定性等池指标。新因子可能与现有因子重复，单项IC虽高却不改善组合，因此边际池收益≤0会被拒绝。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="94" customHeight="1">
+          <t xml:space="preserve">先用近期约126个交易日的数据，通过“非负岭回归”给池内各因子拟合组合权重：权重不能小于零，太大的权重还会受到惩罚。把因子按权重相加成Meta-alpha，再算整池IC、RankIC和多样性/稳定性得分。新因子单独IC好却与旧因子重复，也可能不增加整池价值。用数字和图讲清楚：https://github.com/epshoron/JXwork/blob/main/papers/P005/P005_NONNEGATIVE_RIDGE_GUIDE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="88" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">质量检查与评分层次</t>
@@ -233,7 +233,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="94" customHeight="1">
+    <row r="10" ht="100" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">池状态具体怎样更新？</t>
@@ -250,7 +250,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="94" customHeight="1">
+    <row r="11" ht="88" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">多轮反馈怎么闭环？</t>
@@ -267,7 +267,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="94" customHeight="1">
+    <row r="12" ht="100" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">调度与优化对象</t>
@@ -284,7 +284,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="108" customHeight="1">
+    <row r="13" ht="112" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">GRPO本质是什么？</t>
@@ -301,7 +301,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="94" customHeight="1">
+    <row r="14" ht="88" customHeight="1">
       <c r="A14" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">训练和实际使用怎样区分？</t>
@@ -318,7 +318,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="82" customHeight="1">
+    <row r="15" ht="88" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">公开实现与复现边界</t>
@@ -337,5 +337,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C15"/>
+  <hyperlinks>
+    <hyperlink ref="C8" r:id="rId1" tooltip="查看详细机制图解"/>
+  </hyperlinks>
 </worksheet>
 </file>
--- a/papers/P005/P005_工程复现问题清单_v1.xlsx
+++ b/papers/P005/P005_工程复现问题清单_v1.xlsx
@@ -30,13 +30,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF122C45"/>
+        <fgColor rgb="FF172D48"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F5FA"/>
+        <fgColor rgb="FFF2F5F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -55,13 +55,13 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -72,15 +72,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="94" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="3" max="3" width="98" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">主题</t>
@@ -97,248 +97,214 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="88" customHeight="1">
+    <row r="2" ht="86" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">市场环境究竟是什么？</t>
+          <t xml:space="preserve">市场描述与LLM分工</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">是行情网页、新闻还是市场状态描述？内容从哪里来？</t>
+          <t xml:space="preserve">所谓市场环境来自哪里？两个LLM分别做什么？</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">不是网页，也不是原始K线全文。系统先汇总当时可知的收益、波动、上涨股票占比、量能、板块轮动等数值指标（短10/中63/长252日），再用Llama-3.3-70B-Instruct（温度0）转成“短期/中期/长期/总体”四段英文市场描述，供LLM参考。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="88" customHeight="1">
+          <t xml:space="preserve">程序先按10/63/252日统计涨跌、波动、上涨股占比、成交量和板块轮动，再由Llama-3.3-70B-Instruct转为短/中/长期与总体文字描述；不是网页或原始K线。Qwen3-4B才负责多轮因子搜索，并在离线GRPO中更新权重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="86" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LLM底座与职责</t>
+          <t xml:space="preserve">Prompt与当前因子池</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">市场环境解释和因子生成用的是同一个模型吗？</t>
+          <t xml:space="preserve">市场描述怎样与因子池结合？池里实际存什么？</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">两者分工不同：Llama-3.3-70B-Instruct把市场数值统计整理成语言描述；负责多轮因子提案、工具交互和搜索策略的是Qwen3-4B，后者通过离线GRPO更新参数，测试日只执行固定模型策略。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="100" customHeight="1">
+          <t xml:space="preserve">每日Prompt并列提供市场描述q_t、当前保留因子清单S_t、可用DSL算子及时间窗口。因子池由程序保存和更新，反馈摘要含成员公式、类别、池分及单因子IC/RankIC；这不是股票池，也不是先把市场和池算成一个数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">市场信息怎样与因子池结合？</t>
+          <t xml:space="preserve">初始任务与因子生成形式</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">市场描述和当前因子池是一起写进Prompt吗？</t>
+          <t xml:space="preserve">与P001研究假设、P002 Python函数相比，P005到底输入和输出什么？</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">是，但各有用途：每日User Prompt填写市场文字q_t、种子或前日沿用因子清单S_t、可用DSL算子O及时间窗口；System Prompt约束工具和表达式。进入多轮后，当前保留池摘要和最近尝试记录再作为反馈文本给LLM；不是把两者先算成一个神秘的数值特征。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="88" customHeight="1">
+          <t xml:space="preserve">Qwen3-4B根据市场描述、当前池和DSL规则，每轮提出多个**DSL因子公式与类别标签**；由外部工具执行、评价，不直接生成完整Python交易系统。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">当前因子池指什么？</t>
+          <t xml:space="preserve">池级边际贡献的计算单位</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">“当前因子池”里实际保存的是什么？</t>
+          <t xml:space="preserve">是单个因子的边际，还是一次加入整批因子的增量？</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">是程序维护的Retained Factor Pool（当前保留的因子集合），初始可来自种子/前日沿用因子，之后随测试结果改变。反馈给LLM的摘要含池评分、成员公式、因子类别、单因子分数、IC和RankIC；它不等于股票池或一张行情页面。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="88" customHeight="1">
+          <t xml:space="preserve">一次可提出多个候选，但Pool Updater**逐个**决定：比较加入前后整池分数ΔΓ=Γ(P∪{f})−Γ(P)；满池则试替换。操作单位是单因子，评价对象是整池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="106" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">初始任务与因子生成形式</t>
+          <t xml:space="preserve">整个池怎么得到分数？</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">与P001研究假设、P002 Python函数相比，P005到底输入和输出什么？</t>
+          <t xml:space="preserve">为何加入一个好因子反而可能被拒绝？</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">每天以市场描述q_t、保留因子池S_t与DSL算子/时窗定义搜索上下文，而非要求人工逐条给出Research Idea；Qwen3-4B每轮提出若干DSL因子公式和类别标签，之后由工具执行与打分，不是生成一整份Python工程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="88" customHeight="1">
+          <t xml:space="preserve">先用近期约126个交易日的数据，通过“非负岭回归”给池内各因子拟合组合权重：权重不能小于零，太大的权重还会受到惩罚。把因子按权重相加成Meta-alpha，再算整池IC、RankIC和多样性/稳定性得分。新因子单独IC好却与旧因子重复，也可能不增加整池价值。用数字和图讲清楚：https://github.com/epshoron/JXwork/blob/main/papers/P005/P005_NONNEGATIVE_RIDGE_GUIDE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">池级边际贡献的计算单位</t>
+          <t xml:space="preserve">质量检查与评分层次</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">是单个因子的边际，还是一次加入整批因子的增量？</t>
+          <t xml:space="preserve">什么检查先于池级边际决定，如何区分有效因子和有价值入池？</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">每轮可一次提出多个候选，但Pool Updater逐个判断：计算“加入当前候选前后”整池得分变化ΔΓ=Γ(P∪{f})−Γ(P)（满池则比较替换某成员后的变化）。所以操作单位是单候选，评价对象是整池；不能把单因子IC高直接等同于值得保留。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="124" customHeight="1">
+          <t xml:space="preserve">factor_evaluator先查DSL合法性、可执行性、覆盖率及单因子IC/RankIC/稳定性；Pool Updater再看它能否改善整个池。能计算不等于值得入池。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">整个池怎么得到分数？</t>
+          <t xml:space="preserve">池状态具体怎样更新？</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">为何加入一个好因子反而可能被拒绝？</t>
+          <t xml:space="preserve">谁执行接收、剔除、替换？是LLM自己做吗？</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">先用近期约126个交易日的数据，通过“非负岭回归”给池内各因子拟合组合权重：权重不能小于零，太大的权重还会受到惩罚。把因子按权重相加成Meta-alpha，再算整池IC、RankIC和多样性/稳定性得分。新因子单独IC好却与旧因子重复，也可能不增加整池价值。用数字和图讲清楚：https://github.com/epshoron/JXwork/blob/main/papers/P005/P005_NONNEGATIVE_RIDGE_GUIDE.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="88" customHeight="1">
+          <t xml:space="preserve">LLM提出公式→factor_evaluator筛掉无效候选→Pool Updater按ΔΓ加入、拒绝或在满池时替换弱/冗余成员。改的是外部因子池，而不是LLM权重。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">质量检查与评分层次</t>
+          <t xml:space="preserve">多轮反馈怎么闭环？</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">什么检查先于池级边际决定，如何区分有效因子和有价值入池？</t>
+          <t xml:space="preserve">更新池后，下一轮LLM到底看见什么？</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">factor_evaluator先校验DSL语法与计算可行性、覆盖率及近期单因子IC/RankIC/稳定性；Pool Updater再判断新增候选是否提升整体加权池表现。单候选可用不等于值得入池，不能把两层评分混为一谈。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="100" customHeight="1">
+          <t xml:space="preserve">下一轮Prompt接收当轮候选的评分/接纳情况/边际变化、最近尝试FIFO列表、当前池成员和池分；LLM据此修改后续提案。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">池状态具体怎样更新？</t>
+          <t xml:space="preserve">调度与优化对象</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">谁执行接收、剔除、替换？是LLM自己做吗？</t>
+          <t xml:space="preserve">P005会像P006那样用Bandit决定改因子还是改预测模型吗？</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">LLM提出DSL公式及类别→factor_evaluator语法校验、运行并算单因子IC/RankIC/稳定性/覆盖率→外部Pool Updater先过滤无效候选，再按ΔΓ选择加入/拒绝；满池则尝试替换最弱或最冗余成员。更新的是程序管理的因子列表，不是LLM参数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="88" customHeight="1">
+          <t xml:space="preserve">系统只搜索DSL因子并维护组合池，没有P006式Factor/Model双臂Bandit；但离线GRPO会训练Qwen3-4B的搜索策略。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="86" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">多轮反馈怎么闭环？</t>
+          <t xml:space="preserve">GRPO本质是什么？</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更新池后，下一轮LLM到底看见什么？</t>
+          <t xml:space="preserve">GRPO（你写的GPRO）具体如何学习，改的是哪里？</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">工具把三类文本反馈接回对话：①当轮每个候选的评分、接收/拒绝、边际提升与相似度；②最近尝试过的因子FIFO记录；③当前池的成员和池得分。下一轮LLM据此继续生成或修改，而非盲目重复第一次Prompt。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="100" customHeight="1">
+          <t xml:space="preserve">对同一历史情境采样多条完整“提出因子→工具测试→改池”轨迹，用最终因子池在未来窗口的IC/RankIC给整条轨迹奖励；组内比较后进行梯度更新，让Qwen3-4B更倾向好轨迹。无需单独Critic，不是只改Prompt。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="78" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">调度与优化对象</t>
+          <t xml:space="preserve">训练和实际使用怎样区分？</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">P005会像P006那样用Bandit决定改因子还是改预测模型吗？</t>
+          <t xml:space="preserve">既然用未来收益打分，会不会在每天预测时偷看未来？</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">不会。P005的Qwen3-4B多轮提出DSL因子和工具调用，Pool Updater按池级边际贡献增删候选；外部代码执行筛选，离线GRPO优化LLM的搜索策略参数。没有P006式二臂Factor/Model调度器，也不让LLM交替研发独立的下游预测模型架构。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="112" customHeight="1">
+          <t xml:space="preserve">离线训练可事后利用未来21/63日收益构造奖励；测试日只使用当日已知市场描述与历史数据，固定训练后的LLM权重，日内仍可更新保留因子池；尚无独立代码级泄漏审计。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GRPO本质是什么？</t>
+          <t xml:space="preserve">公开实现与复现边界</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GRPO（你写的GPRO）具体如何学习，改的是哪里？</t>
+          <t xml:space="preserve">这是实际跑通的源码结论，还是论文叙述？</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GRPO=Group Relative Policy Optimization，组相对策略优化。对同一历史市场情境采样多条完整“提议→工具→改池”轨迹；用各轨迹最终因子池在未来窗口的组合IC/RankIC构造奖励，按组内相对成绩形成优势，再通过梯度优化提高好轨迹的生成概率。不训练单独Critic；离线阶段真正更新Qwen3-4B的模型参数。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="88" customHeight="1">
-      <c r="A14" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">训练和实际使用怎样区分？</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">既然用未来收益打分，会不会在每天预测时偷看未来？</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">训练时允许Reward Manager事后看未来21/63日窗口，监督整条历史搜索轨迹；部署/样本外每个交易日仅输入当日可知市场描述、历史行情与保留池，训练完成的LLM权重保持不变，只更新因子池。以上是论文流程口径，尚未独立运行代码审计。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="88" customHeight="1">
-      <c r="A15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">公开实现与复现边界</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">这是实际跑通的源码结论，还是论文叙述？</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr" s="2">
-        <is>
           <t xml:space="preserve">当前依据AlphaPilot论文§3–5及附录核查输入、工具、池更新与GRPO，尚未核实可直接运行的完整官方工程，更未独立复现训练或回测。论文中的流程不等于源码行为已经验证。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C15"/>
+  <autoFilter ref="A1:C13"/>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" tooltip="查看详细机制图解"/>
+    <hyperlink ref="C6" r:id="rId1" tooltip="打开相关来源或机制图解"/>
   </hyperlinks>
 </worksheet>
 </file>